--- a/nr-rm-useless-schema/ig/StructureDefinition-as-ext-practitionerrole-vitale-accepted.xlsx
+++ b/nr-rm-useless-schema/ig/StructureDefinition-as-ext-practitionerrole-vitale-accepted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T09:03:10+00:00</t>
+    <t>2024-03-19T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-rm-useless-schema/ig/StructureDefinition-as-ext-practitionerrole-vitale-accepted.xlsx
+++ b/nr-rm-useless-schema/ig/StructureDefinition-as-ext-practitionerrole-vitale-accepted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T09:36:51+00:00</t>
+    <t>2024-03-19T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-rm-useless-schema/ig/StructureDefinition-as-ext-practitionerrole-vitale-accepted.xlsx
+++ b/nr-rm-useless-schema/ig/StructureDefinition-as-ext-practitionerrole-vitale-accepted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T09:45:37+00:00</t>
+    <t>2024-03-19T09:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
